--- a/public/templates/examples/A-150-PhysicalAccessReviewRecords-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-150-PhysicalAccessReviewRecords-EXAMPLE-M.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="5">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -242,12 +242,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="876300" cy="876300"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -386,7 +386,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -420,7 +420,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-150-PhysicalAccessReviewRecords-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-150-PhysicalAccessReviewRecords-EXAMPLE-M.xlsx
@@ -4,19 +4,21 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Aptos"/>
@@ -137,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -160,6 +162,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -756,7 +761,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -793,7 +798,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>LOG-001</t>
@@ -830,16 +835,14 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>LOG-002</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
+      <c r="B13" s="10">
+        <v>46069</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
@@ -867,7 +870,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="50.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>LOG-003</t>
@@ -904,16 +907,14 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="50.5" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>LOG-004</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
+      <c r="B15" s="10">
+        <v>46090</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
@@ -984,7 +985,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="66.4" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Reviewed by: Security Coordinator</t>
@@ -1000,13 +1001,11 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
+      <c r="D22" s="10">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="23" ht="50.5" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Approved by: Director</t>
@@ -1022,10 +1021,8 @@
           <t>Anthony Reyes</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
+      <c r="D23" s="10">
+        <v>46083</v>
       </c>
     </row>
     <row r="25">
@@ -1105,10 +1102,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
+      <c r="B35" s="10">
+        <v>46083</v>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
@@ -1147,8 +1142,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A33:G33"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>